--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.03704373460521</v>
+        <v>2.443519606873346</v>
       </c>
       <c r="D2" t="n">
-        <v>14.54603004869157</v>
+        <v>2.36372988291238</v>
       </c>
       <c r="E2" t="n">
-        <v>23.91003735055907</v>
+        <v>3.885381069465848</v>
       </c>
       <c r="F2" t="n">
-        <v>24.71720163192308</v>
+        <v>4.016545265187501</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.826970074310806</v>
+        <v>0.9468826370755059</v>
       </c>
       <c r="D3" t="n">
-        <v>6.18465843842649</v>
+        <v>1.005006996244305</v>
       </c>
       <c r="E3" t="n">
-        <v>23.91003735055907</v>
+        <v>3.885381069465848</v>
       </c>
       <c r="F3" t="n">
-        <v>24.71720163192308</v>
+        <v>4.016545265187501</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.45350783512395</v>
+        <v>1.861195023207642</v>
       </c>
       <c r="D4" t="n">
-        <v>11.48981795373387</v>
+        <v>1.867095417481754</v>
       </c>
       <c r="E4" t="n">
-        <v>23.91003735055907</v>
+        <v>3.885381069465848</v>
       </c>
       <c r="F4" t="n">
-        <v>24.71720163192308</v>
+        <v>4.016545265187501</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.55179459274858</v>
+        <v>3.502166621321645</v>
       </c>
       <c r="D5" t="n">
-        <v>21.3214238112999</v>
+        <v>3.464731369336234</v>
       </c>
       <c r="E5" t="n">
-        <v>23.91003735055907</v>
+        <v>3.885381069465848</v>
       </c>
       <c r="F5" t="n">
-        <v>24.71720163192308</v>
+        <v>4.016545265187501</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12.88707011916237</v>
+        <v>2.094148894363886</v>
       </c>
       <c r="D6" t="n">
-        <v>12.14042889652596</v>
+        <v>1.972819695685468</v>
       </c>
       <c r="E6" t="n">
-        <v>23.91003735055907</v>
+        <v>3.885381069465848</v>
       </c>
       <c r="F6" t="n">
-        <v>24.71720163192308</v>
+        <v>4.016545265187501</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>1.743956197831444</v>
+        <v>0.2833928821476097</v>
       </c>
       <c r="D7" t="n">
-        <v>2.006932429798715</v>
+        <v>0.3261265198422912</v>
       </c>
       <c r="E7" t="n">
-        <v>23.91003735055907</v>
+        <v>3.885381069465848</v>
       </c>
       <c r="F7" t="n">
-        <v>24.71720163192308</v>
+        <v>4.016545265187501</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.06255486945462</v>
+        <v>2.610165166286375</v>
       </c>
       <c r="D8" t="n">
-        <v>15.87800715175275</v>
+        <v>2.580176162159821</v>
       </c>
       <c r="E8" t="n">
-        <v>23.91003735055907</v>
+        <v>3.885381069465848</v>
       </c>
       <c r="F8" t="n">
-        <v>24.71720163192308</v>
+        <v>4.016545265187501</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.17722736500908</v>
+        <v>4.091299446813975</v>
       </c>
       <c r="D9" t="n">
-        <v>26.25871739873681</v>
+        <v>4.267041577294732</v>
       </c>
       <c r="E9" t="n">
-        <v>23.91003735055907</v>
+        <v>3.885381069465848</v>
       </c>
       <c r="F9" t="n">
-        <v>24.71720163192308</v>
+        <v>4.016545265187501</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>20.30684469285478</v>
+        <v>3.299862262588903</v>
       </c>
       <c r="D10" t="n">
-        <v>20.0962552455017</v>
+        <v>3.265641477394026</v>
       </c>
       <c r="E10" t="n">
-        <v>23.91003735055907</v>
+        <v>3.885381069465848</v>
       </c>
       <c r="F10" t="n">
-        <v>24.71720163192308</v>
+        <v>4.016545265187501</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>6.565469470648067</v>
+        <v>1.066888788980311</v>
       </c>
       <c r="D11" t="n">
-        <v>6.45023026587047</v>
+        <v>1.048162418203952</v>
       </c>
       <c r="E11" t="n">
-        <v>23.91003735055907</v>
+        <v>3.885381069465848</v>
       </c>
       <c r="F11" t="n">
-        <v>24.71720163192308</v>
+        <v>4.016545265187501</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>77.51752237995022</v>
+        <v>12.59659738674191</v>
       </c>
       <c r="D12" t="n">
-        <v>79.72645791370317</v>
+        <v>12.95554941097677</v>
       </c>
       <c r="E12" t="n">
-        <v>23.91003735055907</v>
+        <v>3.885381069465848</v>
       </c>
       <c r="F12" t="n">
-        <v>24.71720163192308</v>
+        <v>4.016545265187501</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>73.20740186714222</v>
+        <v>11.89620280341061</v>
       </c>
       <c r="D13" t="n">
-        <v>75.35902069378814</v>
+        <v>12.24584086274057</v>
       </c>
       <c r="E13" t="n">
-        <v>23.91003735055907</v>
+        <v>3.885381069465848</v>
       </c>
       <c r="F13" t="n">
-        <v>24.71720163192308</v>
+        <v>4.016545265187501</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
